--- a/results/q2/结果提交_Q2.xlsx
+++ b/results/q2/结果提交_Q2.xlsx
@@ -1330,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
   <cols>
     <col width="12" customWidth="1" style="3" min="1" max="2"/>
@@ -1393,17 +1393,17 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>C-BAT-01</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
@@ -1411,14 +1411,14 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1845.697859216596</v>
+        <v>1560.169078176492</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>2.130694681397041</v>
+        <v>2.917546858512244</v>
       </c>
     </row>
     <row r="3">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>C-BAT-01</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
@@ -1447,14 +1447,14 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>S006</t>
+          <t>S012</t>
         </is>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1565.725652208688</v>
+        <v>1942.964780625902</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2.599686735707714</v>
+        <v>2.760456447566475</v>
       </c>
     </row>
     <row r="4">
@@ -1555,14 +1555,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S012</t>
+          <t>S010</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3444.006456027822</v>
+        <v>3056.421244980191</v>
       </c>
       <c r="H6" t="n">
-        <v>2.760456447566475</v>
+        <v>1.823152829272353</v>
       </c>
     </row>
     <row r="7">
@@ -1587,18 +1587,18 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1565.725652208688</v>
+        <v>1560.169078176492</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>3257.89473038518</v>
+        <v>3540.056357498599</v>
       </c>
       <c r="H7" t="n">
-        <v>2.995733438084778</v>
+        <v>5.250173078792301</v>
       </c>
     </row>
     <row r="8">
@@ -1609,21 +1609,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C-BAT-04</t>
+          <t>A-BAT-01</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1889.309602037297</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4001.196881359404</v>
+        <v>2007.058270905563</v>
       </c>
       <c r="H8" t="n">
-        <v>5.854736199638475</v>
+        <v>2.921276935382787</v>
       </c>
     </row>
     <row r="9">
@@ -1659,18 +1659,18 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1845.697859216596</v>
+        <v>1942.964780625902</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>S010</t>
+          <t>S014</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3401.077428794866</v>
+        <v>3788.662639842498</v>
       </c>
       <c r="H9" t="n">
-        <v>1.823152829272353</v>
+        <v>2.130694681397041</v>
       </c>
     </row>
     <row r="10">
@@ -1681,21 +1681,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C-BAT-01</t>
+          <t>A-BAT-02</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3257.89473038518</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4752.063808561671</v>
+        <v>1190.899503136468</v>
       </c>
       <c r="H10" t="n">
-        <v>2.917546858512244</v>
+        <v>1.219501901927791</v>
       </c>
     </row>
     <row r="11">
@@ -1727,22 +1727,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C-BAT-02</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4001.196881359404</v>
+        <v>1889.309602037297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S004</t>
+          <t>S006</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6302.253573885432</v>
+        <v>3455.035254245985</v>
       </c>
       <c r="H11" t="n">
-        <v>6.152871596056126</v>
+        <v>2.599686735707714</v>
       </c>
     </row>
     <row r="12">
@@ -1753,32 +1753,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B-BAT-02</t>
+          <t>C-BAT-01</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3401.077428794866</v>
+        <v>3455.035254245985</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4589.497901601419</v>
+        <v>5332.225778564598</v>
       </c>
       <c r="H12" t="n">
-        <v>1.073925269939636</v>
+        <v>4.222147882156408</v>
       </c>
     </row>
     <row r="13">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U07</t>
+          <t>U03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C-BAT-03</t>
+          <t>A-BAT-03</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4902.572536533141</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>S008</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>7092.642919377684</v>
+        <v>1250.899503136468</v>
       </c>
       <c r="H13" t="n">
-        <v>5.832225181246579</v>
+        <v>1.282320710525659</v>
       </c>
     </row>
     <row r="14">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U08</t>
+          <t>U07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1835,22 +1835,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C-BAT-01</t>
+          <t>C-BAT-02</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6375.566082742071</v>
+        <v>3644.486753915256</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S008</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>8745.657452447291</v>
+        <v>5834.5571367598</v>
       </c>
       <c r="H14" t="n">
-        <v>5.764874419169901</v>
+        <v>5.832225181246579</v>
       </c>
     </row>
     <row r="15">
@@ -1871,22 +1871,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B-BAT-01</t>
+          <t>B-BAT-02</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3444.006456027822</v>
+        <v>3056.421244980191</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>S003</t>
+          <t>S011</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5524.529779671844</v>
+        <v>4244.841717786744</v>
       </c>
       <c r="H15" t="n">
-        <v>2.779848267267533</v>
+        <v>1.073925269939636</v>
       </c>
     </row>
     <row r="16">
@@ -1897,32 +1897,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U01</t>
+          <t>U05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>A-BAT-01</t>
+          <t>B-BAT-01</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>3805.829241238041</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S003</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2007.058270905563</v>
+        <v>5886.352564882063</v>
       </c>
       <c r="H16" t="n">
-        <v>3.020048854217715</v>
+        <v>2.779848267267533</v>
       </c>
     </row>
     <row r="17">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U05</t>
+          <t>U08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B-BAT-04</t>
+          <t>C-BAT-04</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4857.776988146219</v>
+        <v>5332.225778564598</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>S009</t>
+          <t>S004</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>6416.218726828517</v>
+        <v>7633.282471090627</v>
       </c>
       <c r="H17" t="n">
-        <v>2.096209183314957</v>
+        <v>6.152871596056126</v>
       </c>
     </row>
     <row r="18">
@@ -1969,32 +1969,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U06</t>
+          <t>U04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B-BAT-03</t>
+          <t>A-BAT-04</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5524.529779671844</v>
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>S015</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>7352.806429257412</v>
+        <v>1190.899503136468</v>
       </c>
       <c r="H18" t="n">
-        <v>2.307393025297905</v>
+        <v>1.219501901927791</v>
       </c>
     </row>
     <row r="19">
@@ -2005,32 +2005,212 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>U06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>B-BAT-03</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4513.120804331544</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S015</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>6341.397453917111</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.307393025297905</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Q2-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>U07</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>C-BAT-04</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>7092.642919377684</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>S005</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>8969.833443696296</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4.222147882156408</v>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>C-BAT-03</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5834.5571367598</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S001;S009</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>8003.278303575325</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.103581209451868</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Q2-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>U02</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A-BAT-05</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1190.899503136468</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>3393.528807024179</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.93144520279479</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Q2-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>U04</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>A-BAT-06</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1190.899503136468</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>3453.528807024179</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.083521008838739</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q2-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>U01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>A-BAT-02</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2043.200052582274</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S002</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>4050.258323487837</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.020048854217715</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q2-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>U05</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>B-BAT-02</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5886.352564882063</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S003</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>7906.875888526085</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.585418568982548</v>
       </c>
     </row>
   </sheetData>
@@ -2083,7 +2263,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -2092,7 +2272,7 @@
         </is>
       </c>
       <c r="D2" s="4" t="n">
-        <v>2945.995191296934</v>
+        <v>908.5730849015672</v>
       </c>
     </row>
     <row r="3">
@@ -2103,7 +2283,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -2112,7 +2292,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>2945.995191296934</v>
+        <v>6974.826675848046</v>
       </c>
     </row>
     <row r="4">
@@ -2123,7 +2303,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2132,7 +2312,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2945.995191296934</v>
+        <v>6974.826675848046</v>
       </c>
     </row>
     <row r="5">
@@ -2143,7 +2323,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2152,7 +2332,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2945.995191296934</v>
+        <v>6974.826675848046</v>
       </c>
     </row>
     <row r="6">
@@ -2163,7 +2343,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2172,7 +2352,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4440.164269473426</v>
+        <v>6974.826675848046</v>
       </c>
     </row>
     <row r="7">
@@ -2183,7 +2363,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2192,7 +2372,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2945.995191296934</v>
+        <v>1248.269539088246</v>
       </c>
     </row>
     <row r="8">
@@ -2203,7 +2383,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2212,7 +2392,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2945.995191296934</v>
+        <v>1248.269539088246</v>
       </c>
     </row>
     <row r="9">
@@ -2223,7 +2403,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2232,7 +2412,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2945.995191296934</v>
+        <v>1248.269539088246</v>
       </c>
     </row>
     <row r="10">
@@ -2243,7 +2423,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-012</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2252,7 +2432,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4440.164269473426</v>
+        <v>908.5730849015672</v>
       </c>
     </row>
     <row r="11">
@@ -2263,7 +2443,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2272,7 +2452,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2945.995191296934</v>
+        <v>1248.269539088246</v>
       </c>
     </row>
     <row r="12">
@@ -2283,7 +2463,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2292,7 +2472,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4440.164269473426</v>
+        <v>1248.269539088246</v>
       </c>
     </row>
     <row r="13">
@@ -2303,7 +2483,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Q2-006</t>
+          <t>Q2-009</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2312,7 +2492,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2945.995191296934</v>
+        <v>848.5730849015672</v>
       </c>
     </row>
     <row r="14">
@@ -2323,7 +2503,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2332,7 +2512,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4440.164269473426</v>
+        <v>1248.269539088246</v>
       </c>
     </row>
     <row r="15">
@@ -2343,7 +2523,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-017</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2352,7 +2532,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4440.164269473426</v>
+        <v>848.5730849015672</v>
       </c>
     </row>
     <row r="16">
@@ -2363,7 +2543,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Q2-009</t>
+          <t>Q2-001</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2372,7 +2552,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4440.164269473426</v>
+        <v>1248.269539088246</v>
       </c>
     </row>
     <row r="17">
@@ -2383,7 +2563,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2392,7 +2572,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3378.66324169835</v>
+        <v>3328.669188035055</v>
       </c>
     </row>
     <row r="18">
@@ -2403,7 +2583,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2412,7 +2592,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1285.469135452781</v>
+        <v>2917.522717837545</v>
       </c>
     </row>
     <row r="19">
@@ -2423,7 +2603,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2432,7 +2612,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3378.66324169835</v>
+        <v>2917.522717837545</v>
       </c>
     </row>
     <row r="20">
@@ -2452,7 +2632,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3378.66324169835</v>
+        <v>1285.469135452781</v>
       </c>
     </row>
     <row r="21">
@@ -2463,7 +2643,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2472,7 +2652,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3378.66324169835</v>
+        <v>2917.522717837545</v>
       </c>
     </row>
     <row r="22">
@@ -2483,7 +2663,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Q2-015</t>
+          <t>Q2-022</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2492,7 +2672,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1285.469135452781</v>
+        <v>3328.669188035055</v>
       </c>
     </row>
     <row r="23">
@@ -2512,7 +2692,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3378.66324169835</v>
+        <v>1285.469135452781</v>
       </c>
     </row>
     <row r="24">
@@ -2523,7 +2703,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Q2-007</t>
+          <t>Q2-006</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2532,7 +2712,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3378.66324169835</v>
+        <v>2917.522717837545</v>
       </c>
     </row>
     <row r="25">
@@ -2543,7 +2723,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2552,7 +2732,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7955.071767594681</v>
+        <v>5154.064236393385</v>
       </c>
     </row>
     <row r="26">
@@ -2563,7 +2743,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2572,7 +2752,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4792.241451183167</v>
+        <v>2600.187488413656</v>
       </c>
     </row>
     <row r="27">
@@ -2583,7 +2763,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2592,7 +2772,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7955.071767594681</v>
+        <v>7174.587560037407</v>
       </c>
     </row>
     <row r="28">
@@ -2603,7 +2783,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2612,7 +2792,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4792.241451183167</v>
+        <v>5154.064236393385</v>
       </c>
     </row>
     <row r="29">
@@ -2623,7 +2803,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Q2-014</t>
+          <t>Q2-015</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2632,7 +2812,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4792.241451183167</v>
+        <v>5154.064236393385</v>
       </c>
     </row>
     <row r="30">
@@ -2643,7 +2823,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-023</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2652,7 +2832,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7955.071767594681</v>
+        <v>7174.587560037407</v>
       </c>
     </row>
     <row r="31">
@@ -2663,7 +2843,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-020</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2672,7 +2852,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7955.071767594681</v>
+        <v>2540.187488413656</v>
       </c>
     </row>
     <row r="32">
@@ -2683,7 +2863,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Q2-013</t>
+          <t>Q2-021</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2692,7 +2872,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7955.071767594681</v>
+        <v>2600.187488413656</v>
       </c>
     </row>
     <row r="33">
@@ -2703,7 +2883,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2712,7 +2892,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5584.695227622417</v>
+        <v>6915.724124827612</v>
       </c>
     </row>
     <row r="34">
@@ -2723,7 +2903,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2732,7 +2912,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>5584.695227622417</v>
+        <v>6915.724124827612</v>
       </c>
     </row>
     <row r="35">
@@ -2743,7 +2923,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2752,7 +2932,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5584.695227622417</v>
+        <v>6915.724124827612</v>
       </c>
     </row>
     <row r="36">
@@ -2763,7 +2943,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2772,7 +2952,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5584.695227622417</v>
+        <v>6915.724124827612</v>
       </c>
     </row>
     <row r="37">
@@ -2783,7 +2963,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2792,7 +2972,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5584.695227622417</v>
+        <v>6915.724124827612</v>
       </c>
     </row>
     <row r="38">
@@ -2803,7 +2983,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Q2-010</t>
+          <t>Q2-016</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2812,7 +2992,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5584.695227622417</v>
+        <v>6915.724124827612</v>
       </c>
     </row>
     <row r="39">
@@ -2823,7 +3003,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2832,7 +3012,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8465.87318153699</v>
+        <v>4828.265516405291</v>
       </c>
     </row>
     <row r="40">
@@ -2843,7 +3023,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2852,7 +3032,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8465.87318153699</v>
+        <v>4828.265516405291</v>
       </c>
     </row>
     <row r="41">
@@ -2863,7 +3043,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2872,7 +3052,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8465.87318153699</v>
+        <v>4828.265516405291</v>
       </c>
     </row>
     <row r="42">
@@ -2883,7 +3063,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2892,7 +3072,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8465.87318153699</v>
+        <v>4828.265516405291</v>
       </c>
     </row>
     <row r="43">
@@ -2903,7 +3083,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2912,7 +3092,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8465.87318153699</v>
+        <v>4828.265516405291</v>
       </c>
     </row>
     <row r="44">
@@ -2923,7 +3103,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Q2-018</t>
+          <t>Q2-011</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2932,7 +3112,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8465.87318153699</v>
+        <v>4828.265516405291</v>
       </c>
     </row>
     <row r="45">
@@ -2943,7 +3123,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2952,7 +3132,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1211.507826104344</v>
+        <v>3100.817428141641</v>
       </c>
     </row>
     <row r="46">
@@ -2963,7 +3143,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2972,7 +3152,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1211.507826104344</v>
+        <v>3100.817428141641</v>
       </c>
     </row>
     <row r="47">
@@ -2983,7 +3163,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2992,7 +3172,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1211.507826104344</v>
+        <v>3100.817428141641</v>
       </c>
     </row>
     <row r="48">
@@ -3003,7 +3183,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3012,7 +3192,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1211.507826104344</v>
+        <v>3100.817428141641</v>
       </c>
     </row>
     <row r="49">
@@ -3023,7 +3203,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3032,7 +3212,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1211.507826104344</v>
+        <v>3100.817428141641</v>
       </c>
     </row>
     <row r="50">
@@ -3043,7 +3223,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Q2-002</t>
+          <t>Q2-010</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3052,7 +3232,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1211.507826104344</v>
+        <v>3100.817428141641</v>
       </c>
     </row>
     <row r="51">
@@ -3163,7 +3343,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3172,7 +3352,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6395.447727955412</v>
+        <v>5137.361945337528</v>
       </c>
     </row>
     <row r="57">
@@ -3183,7 +3363,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3192,7 +3372,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>6395.447727955412</v>
+        <v>5137.361945337528</v>
       </c>
     </row>
     <row r="58">
@@ -3203,7 +3383,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3212,7 +3392,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6395.447727955412</v>
+        <v>5137.361945337528</v>
       </c>
     </row>
     <row r="59">
@@ -3223,7 +3403,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -3232,7 +3412,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6395.447727955412</v>
+        <v>5137.361945337528</v>
       </c>
     </row>
     <row r="60">
@@ -3243,7 +3423,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Q2-012</t>
+          <t>Q2-013</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -3252,7 +3432,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6395.447727955412</v>
+        <v>5137.361945337528</v>
       </c>
     </row>
     <row r="61">
@@ -3263,7 +3443,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3272,7 +3452,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5948.587857487368</v>
+        <v>7514.879282175256</v>
       </c>
     </row>
     <row r="62">
@@ -3283,7 +3463,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3292,7 +3472,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5948.587857487368</v>
+        <v>7514.879282175256</v>
       </c>
     </row>
     <row r="63">
@@ -3303,7 +3483,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Q2-016</t>
+          <t>Q2-019</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3312,7 +3492,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5948.587857487368</v>
+        <v>7514.879282175256</v>
       </c>
     </row>
     <row r="64">
@@ -3323,7 +3503,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -3332,7 +3512,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2930.924310672397</v>
+        <v>2586.268126857723</v>
       </c>
     </row>
     <row r="65">
@@ -3343,7 +3523,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3352,7 +3532,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2930.924310672397</v>
+        <v>2586.268126857723</v>
       </c>
     </row>
     <row r="66">
@@ -3363,7 +3543,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Q2-008</t>
+          <t>Q2-005</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3372,7 +3552,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2930.924310672397</v>
+        <v>2586.268126857723</v>
       </c>
     </row>
     <row r="67">
@@ -3383,7 +3563,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3392,7 +3572,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>4307.474331864809</v>
+        <v>3962.818148050134</v>
       </c>
     </row>
     <row r="68">
@@ -3403,7 +3583,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3412,7 +3592,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>4307.474331864809</v>
+        <v>3962.818148050134</v>
       </c>
     </row>
     <row r="69">
@@ -3423,7 +3603,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Q2-011</t>
+          <t>Q2-014</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3432,7 +3612,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4307.474331864809</v>
+        <v>3962.818148050134</v>
       </c>
     </row>
     <row r="70">
@@ -3443,7 +3623,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-002</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3452,7 +3632,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2782.454065714872</v>
+        <v>1281.412390312951</v>
       </c>
     </row>
     <row r="71">
@@ -3463,7 +3643,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-002</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3472,7 +3652,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2782.454065714872</v>
+        <v>1281.412390312951</v>
       </c>
     </row>
     <row r="72">
@@ -3483,7 +3663,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Q2-005</t>
+          <t>Q2-002</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3492,7 +3672,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>2782.454065714872</v>
+        <v>1281.412390312951</v>
       </c>
     </row>
     <row r="73">
@@ -3563,7 +3743,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3572,7 +3752,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1230.405596274965</v>
+        <v>3173.370376900867</v>
       </c>
     </row>
     <row r="77">
@@ -3583,7 +3763,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3592,7 +3772,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1230.405596274965</v>
+        <v>3173.370376900867</v>
       </c>
     </row>
     <row r="78">
@@ -3603,7 +3783,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Q2-001</t>
+          <t>Q2-008</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -3612,7 +3792,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1230.405596274965</v>
+        <v>3173.370376900867</v>
       </c>
     </row>
     <row r="79">
@@ -3623,7 +3803,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3632,7 +3812,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6742.108104464628</v>
+        <v>5730.699129124328</v>
       </c>
     </row>
     <row r="80">
@@ -3643,7 +3823,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3652,7 +3832,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>6742.108104464628</v>
+        <v>5730.699129124328</v>
       </c>
     </row>
     <row r="81">
@@ -3663,7 +3843,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Q2-017</t>
+          <t>Q2-018</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3672,7 +3852,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6742.108104464628</v>
+        <v>5730.699129124328</v>
       </c>
     </row>
   </sheetData>
